--- a/从零开始学Slots/从零开始学Slots-45-实战篇-SuperNiubi.xlsx
+++ b/从零开始学Slots/从零开始学Slots-45-实战篇-SuperNiubi.xlsx
@@ -8917,6 +8917,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N177" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -9658,5 +9661,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:Q74" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-45-实战篇-SuperNiubi.xlsx
+++ b/从零开始学Slots/从零开始学Slots-45-实战篇-SuperNiubi.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="225">
   <si>
     <r>
       <rPr>
@@ -7408,12 +7408,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
     <numFmt numFmtId="166" formatCode="0.0000%"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.00%"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -7590,7 +7591,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7729,6 +7730,14 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -9472,8 +9481,8 @@
       <c r="E40" s="16"/>
     </row>
     <row r="41" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15" t="s">
-        <v>200</v>
+      <c r="A41" s="35">
+        <v>28</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>201</v>
@@ -9499,8 +9508,8 @@
       <c r="A43" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="B43" s="15" t="s">
-        <v>207</v>
+      <c r="B43" s="36">
+        <v>0.9642</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>208</v>
@@ -9511,8 +9520,8 @@
       <c r="A44" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="B44" s="15" t="s">
-        <v>210</v>
+      <c r="B44" s="36">
+        <v>0.9677</v>
       </c>
       <c r="C44" s="16" t="s">
         <v>211</v>

--- a/从零开始学Slots/从零开始学Slots-45-实战篇-SuperNiubi.xlsx
+++ b/从零开始学Slots/从零开始学Slots-45-实战篇-SuperNiubi.xlsx
@@ -7408,13 +7408,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
     <numFmt numFmtId="166" formatCode="0.0000%"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.00%"/>
+    <numFmt numFmtId="170" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -7591,7 +7592,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7737,6 +7738,26 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" applyNumberFormat="1" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" applyNumberFormat="1" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" applyNumberFormat="1" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" applyNumberFormat="1" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" applyNumberFormat="1" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9160,7 +9181,7 @@
       <c r="B20" s="17" t="n">
         <v>0.1157</v>
       </c>
-      <c r="C20" s="18" t="n">
+      <c r="C20" s="38" t="n">
         <f aca="false">B20^3</f>
         <v>0.001548816893</v>
       </c>
@@ -9190,7 +9211,7 @@
       <c r="B21" s="17" t="n">
         <v>0.0964</v>
       </c>
-      <c r="C21" s="18" t="n">
+      <c r="C21" s="38" t="n">
         <f aca="false">B21^3</f>
         <v>0.000895841344</v>
       </c>
@@ -9220,7 +9241,7 @@
       <c r="B22" s="17" t="n">
         <v>0.0804</v>
       </c>
-      <c r="C22" s="18" t="n">
+      <c r="C22" s="38" t="n">
         <f aca="false">B22^3</f>
         <v>0.000519718464</v>
       </c>
@@ -9250,7 +9271,7 @@
       <c r="B23" s="17" t="n">
         <v>0.067</v>
       </c>
-      <c r="C23" s="18" t="n">
+      <c r="C23" s="38" t="n">
         <f aca="false">B23^3</f>
         <v>0.000300763</v>
       </c>
@@ -9277,7 +9298,7 @@
       <c r="A24" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="B24" s="23" t="n">
+      <c r="B24" s="39" t="n">
         <f aca="false">1-SUM(B20:B23)</f>
         <v>0.6405</v>
       </c>
@@ -9301,7 +9322,7 @@
       <c r="A25" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="B25" s="23" t="n">
+      <c r="B25" s="39" t="n">
         <f aca="false">SUM(B20:B23)+B24</f>
         <v>1</v>
       </c>
